--- a/education_forms/027_market_structures_assessment--education_forms.xlsx
+++ b/education_forms/027_market_structures_assessment--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>_goals_</t>
+          <t>goals</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>_goals_</t>
+          <t>goals</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>price_equilibrium</t>
+          <t>price equilibrium</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>market_failures</t>
+          <t>market failures</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>market_structures</t>
+          <t>market structures</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'_goals_'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '_goals_'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>price_equilibrium</t>
+          <t>price equilibrium</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>market_failures</t>
+          <t>market failures</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>market_structures</t>
+          <t>market structures</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>price_equilibrium</t>
+          <t>price equilibrium</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>market_failures</t>
+          <t>market failures</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>market_structures</t>
+          <t>market structures</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>_goals_</t>
+          <t>goals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>_goals_</t>
+          <t>goals</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>price_equilibrium</t>
+          <t>price equilibrium</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>market_failures</t>
+          <t>market failures</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>market_structures</t>
+          <t>market structures</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>price_equilibrium</t>
+          <t>price equilibrium</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>market_failures</t>
+          <t>market failures</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>market_structures</t>
+          <t>market structures</t>
         </is>
       </c>
     </row>
